--- a/docs/test-report-v0.1.xlsx
+++ b/docs/test-report-v0.1.xlsx
@@ -867,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -993,104 +993,126 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>画面での確認</t>
+          <t>GitHub Actions</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>168</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>168</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>未実施は S-14・S-15・S-18</t>
+          <t>push のたびに GitHub の Windows のサーバー(windows-latest)で同じ自動テストを走らせる。初回 2026-10-21:168 passed(1分55秒)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>要件(機能)</t>
+          <t>画面での確認</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>「未実施あり」は自動テストと画面での確認はあるが、本物で確かめていない所が残るもの</t>
+          <t>未実施は S-14・S-15・S-18</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>要件(非機能など)</t>
+          <t>要件(機能)</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>空欄・未実施ありは、止まる1で決める</t>
+          <t>「未実施あり」は自動テストと画面での確認はあるが、本物で確かめていない所が残るもの</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>不具合</t>
+          <t>要件(非機能など)</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>全部直した</t>
+          <t>空欄・未実施ありは、止まる1で決める</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
+          <t>不具合</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>全部直した</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
           <t>課題</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr"/>
-      <c r="D19" s="10" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr"/>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/test-report-v0.1.xlsx
+++ b/docs/test-report-v0.1.xlsx
@@ -92,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -114,11 +114,55 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,6 +188,8 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -590,15 +636,15 @@
           <t>作成</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="14" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="C18" s="5" t="inlineStr">
@@ -1023,14 +1069,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="C16" s="10" t="n">
+        <v>22</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>未実施は S-14・S-15・S-18</t>
+          <t>未実施は S-14・S-15</t>
         </is>
       </c>
     </row>
@@ -1045,10 +1089,8 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="C17" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
@@ -7899,12 +7941,12 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>ふだんの使い方で、1行入力と着手日が思ったとおりに読めるか</t>
+          <t>ふだんの使い方で、1行入力と着手日が思ったとおりに読めるか。2026-10-22:1行入力で入れた「卒論」(着手日・締切 10/22)が、トップの「今日」に1回だけ出た(自動のチェックと本人の確認)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>未実施</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8766,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>未実施あり</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8803,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>未実施あり</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -8934,6 +8976,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
